--- a/DataTables/DetailText/剧情/023_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/023_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51238C80-81F5-4606-B358-1105F5C0980F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F85E86B-E7E8-489C-AEB2-9BC3B2EA780E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="67">
   <si>
     <t>LineIndex</t>
   </si>
@@ -129,10 +118,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>hide</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>半夏</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -145,8 +130,20 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <r>
-      <t>先生，</t>
+    <t>您是？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>哦，那姑娘所患的是肺气虚，并无大碍，只是看起来似乎有心事。您可知其中原委？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>哎哟？这里面有事儿，快说来听听。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>小生是姑娘的一位相</t>
     </r>
     <r>
       <rPr>
@@ -156,7 +153,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>刚</t>
+      <t>识</t>
     </r>
     <r>
       <rPr>
@@ -166,25 +163,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>才那姑娘是得了什么病啊？</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>您是？</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>哦，那姑娘所患的是肺气虚，并无大碍，只是看起来似乎有心事。您可知其中原委？</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>哎哟？这里面有事儿，快说来听听。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>小生是姑娘的一位相</t>
+      <t>，担心姑娘身体，来</t>
     </r>
     <r>
       <rPr>
@@ -194,7 +173,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>识</t>
+      <t>问问</t>
     </r>
     <r>
       <rPr>
@@ -204,8 +183,11 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>，担心姑娘身体，来</t>
-    </r>
+      <t>大夫。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -214,7 +196,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>问问</t>
+      <t>实</t>
     </r>
     <r>
       <rPr>
@@ -224,11 +206,8 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>大夫。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
+      <t>不相</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -237,7 +216,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>实</t>
+      <t>瞒</t>
     </r>
     <r>
       <rPr>
@@ -247,7 +226,31 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>不相</t>
+      <t>，小生在柳月坊与</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>飞燕相识，一见倾心，私底下定了终身。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>sick</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>…多谢先生。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>那就多</t>
     </r>
     <r>
       <rPr>
@@ -257,7 +260,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>瞒</t>
+      <t>谢</t>
     </r>
     <r>
       <rPr>
@@ -267,31 +270,13 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>，小生在柳月坊与</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>飞燕相识，一见倾心，私底下定了终身。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>sick</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>…多谢先生。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>那就多</t>
+      <t>大夫了，走吧女儿。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>想必姑娘是因</t>
     </r>
     <r>
       <rPr>
@@ -301,7 +286,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>谢</t>
+      <t>为这</t>
     </r>
     <r>
       <rPr>
@@ -311,13 +296,37 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>大夫了，走吧女儿。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>想必姑娘是因</t>
+      <t>事急坏了身子。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>唉，又是一对儿苦命的鸳鸯。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>吴芷兰</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>我也想</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>帮他们，可怎么帮呢？</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>姑娘</t>
     </r>
     <r>
       <rPr>
@@ -327,7 +336,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>为这</t>
+      <t>这</t>
     </r>
     <r>
       <rPr>
@@ -337,21 +346,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>事急坏了身子。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>唉，又是一对儿苦命的鸳鸯。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>吴芷兰</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>我也想</t>
+      <t>病是肺气虚，平日注意避风避寒，开副</t>
     </r>
     <r>
       <rPr>
@@ -361,23 +356,119 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>帮他们，可怎么帮呢？</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>姑娘</t>
+      <t>补肺汤调养调养。早上练练六字诀中的呬字诀，舒畅胸中气机。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>相公咱想办法帮帮他们吧。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>剧情ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发场景</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发天数</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <r>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱判定</t>
+    </r>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发金钱</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>名望判定</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发名望</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发条目</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发剧情ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发治疗结果</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>播放后</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>人物ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>疾病</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>人物立绘路径</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>cured</t>
+  </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <r>
+      <t>原想着凑够五百两</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这</t>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>银子</t>
     </r>
     <r>
       <rPr>
@@ -387,129 +478,17 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>病是肺气虚，平日注意避风避寒，开副</t>
+      <t>，</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>补肺汤调养调养。早上练练六字诀中的呬字诀，舒畅胸中气机。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>相公咱想办法帮帮他们吧。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>剧情ID</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>剧情名</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>触发场景</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>触发天数</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <r>
-      <t>金</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>钱判定</t>
-    </r>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>触发金钱</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>名望判定</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>触发名望</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>触发条目</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>触发剧情ID</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>触发治疗结果</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>播放后</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>人物ID</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>疾病</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>人物立绘路径</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>奖励金钱</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>奖励名望</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>奖励心得</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>cured</t>
-  </si>
-  <si>
-    <t>Music</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <r>
-      <t>原想着凑够五百两</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>银子</t>
+      <t>给</t>
     </r>
     <r>
       <rPr>
@@ -519,7 +498,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>，</t>
+      <t>她</t>
     </r>
     <r>
       <rPr>
@@ -529,7 +508,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>给</t>
+      <t>赎</t>
     </r>
     <r>
       <rPr>
@@ -539,17 +518,17 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>她</t>
+      <t>身。可那</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>赎</t>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>老鸨</t>
     </r>
     <r>
       <rPr>
@@ -559,7 +538,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>身。可那</t>
+      <t>坐地起价，</t>
     </r>
     <r>
       <rPr>
@@ -569,7 +548,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>老鸨</t>
+      <t>张口就要</t>
     </r>
     <r>
       <rPr>
@@ -579,7 +558,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>坐地起价，</t>
+      <t>一千两，</t>
     </r>
     <r>
       <rPr>
@@ -589,28 +568,52 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>张口就要</t>
-    </r>
+      <t>这让我们上哪去凑这么多银子啊…</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>subtitle</t>
+  </si>
+  <si>
+    <t>收入一两白银</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>一千两，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这让我们上哪去凑这么多银子啊…</t>
-    </r>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>大夫，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>刚</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>才那姑娘是得了什么病啊？</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Background/black.png</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -618,11 +621,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -636,7 +639,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -657,7 +660,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -694,6 +697,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
@@ -760,7 +770,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -839,9 +849,12 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1120,78 +1133,78 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1328125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.1328125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="23" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="23" customFormat="1">
       <c r="A1" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="D1" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="E1" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="F1" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="G1" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="H1" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="I1" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="J1" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="K1" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="L1" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="M1" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="N1" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="M1" s="21" t="s">
+      <c r="O1" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="N1" s="21" t="s">
+      <c r="P1" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="O1" s="21" t="s">
+      <c r="Q1" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="P1" s="21" t="s">
+      <c r="R1" s="21" t="s">
         <v>59</v>
-      </c>
-      <c r="Q1" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="R1" s="21" t="s">
-        <v>61</v>
       </c>
       <c r="S1" s="22" t="s">
         <v>11</v>
@@ -1200,7 +1213,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="23" customFormat="1" ht="18">
+    <row r="2" spans="1:20" s="23" customFormat="1">
       <c r="A2" s="5" t="s">
         <v>15</v>
       </c>
@@ -1220,7 +1233,7 @@
         <v>17</v>
       </c>
       <c r="K2" s="25" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L2" s="25" t="s">
         <v>13</v>
@@ -1228,7 +1241,9 @@
       <c r="M2" s="24"/>
       <c r="N2" s="25"/>
       <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
+      <c r="P2" s="25">
+        <v>1000</v>
+      </c>
       <c r="Q2" s="25"/>
       <c r="R2" s="26"/>
       <c r="S2" s="26" t="b">
@@ -1323,17 +1338,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1363,10 +1378,10 @@
         <v>4</v>
       </c>
       <c r="I1" s="27" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="33">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1385,7 +1400,7 @@
         <v>14</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I2" s="1"/>
     </row>
@@ -1403,12 +1418,12 @@
         <v>9</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I3" s="1"/>
     </row>
@@ -1450,7 +1465,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I5" s="1"/>
     </row>
@@ -1468,12 +1483,10 @@
         <v>22</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I6" s="1"/>
     </row>
@@ -1491,11 +1504,9 @@
         <v>9</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>25</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="1" t="s">
         <v>20</v>
@@ -1507,21 +1518,17 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>22</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="2"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>29</v>
+        <v>66</v>
+      </c>
+      <c r="H8" s="28" t="s">
+        <v>64</v>
       </c>
       <c r="I8" s="1"/>
     </row>
@@ -1532,17 +1539,19 @@
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>18</v>
+      <c r="C9" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3" t="s">
-        <v>30</v>
+      <c r="G9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>65</v>
       </c>
       <c r="I9" s="1"/>
     </row>
@@ -1553,17 +1562,17 @@
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>24</v>
+      <c r="C10" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="I10" s="1"/>
     </row>
@@ -1574,11 +1583,11 @@
       <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>18</v>
+      <c r="C11" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -1595,17 +1604,17 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>26</v>
+      <c r="C12" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I12" s="1"/>
     </row>
@@ -1617,16 +1626,16 @@
         <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="14" t="s">
-        <v>34</v>
+      <c r="H13" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="I13" s="1"/>
     </row>
@@ -1646,8 +1655,8 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="3" t="s">
-        <v>64</v>
+      <c r="H14" s="14" t="s">
+        <v>32</v>
       </c>
       <c r="I14" s="1"/>
     </row>
@@ -1658,17 +1667,17 @@
       <c r="B15" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>18</v>
+      <c r="C15" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="I15" s="1"/>
     </row>
@@ -1679,17 +1688,17 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>26</v>
+      <c r="C16" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I16" s="1"/>
     </row>
@@ -1700,17 +1709,17 @@
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="15" t="s">
-        <v>40</v>
+      <c r="C17" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="15" t="s">
-        <v>43</v>
+      <c r="H17" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="I17" s="1"/>
     </row>
@@ -1721,29 +1730,39 @@
       <c r="B18" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>18</v>
+      <c r="C18" s="15" t="s">
+        <v>38</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="3" t="s">
+      <c r="H18" s="15" t="s">
         <v>41</v>
       </c>
       <c r="I18" s="1"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="2"/>
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
+      <c r="H19" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="I19" s="1"/>
     </row>
     <row r="20" spans="1:9">
@@ -1812,6 +1831,17 @@
       <c r="H25" s="3"/>
       <c r="I25" s="1"/>
     </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="1"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DataTables/DetailText/剧情/023_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/023_02治疗成功.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F85E86B-E7E8-489C-AEB2-9BC3B2EA780E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B1BA4C0-44F6-4230-B45A-D0C5906E4647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="66">
   <si>
     <t>LineIndex</t>
   </si>
@@ -610,10 +610,6 @@
       </rPr>
       <t>才那姑娘是得了什么病啊？</t>
     </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>res://Assets/Background/black.png</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1524,9 +1520,7 @@
       <c r="D8" s="2"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="G8" s="2"/>
       <c r="H8" s="28" t="s">
         <v>64</v>
       </c>
@@ -1547,9 +1541,7 @@
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="G9" s="2"/>
       <c r="H9" s="14" t="s">
         <v>65</v>
       </c>

--- a/DataTables/DetailText/剧情/023_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/023_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B1BA4C0-44F6-4230-B45A-D0C5906E4647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61658A2D-F581-468D-B003-490A4D24D915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,6 +21,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -110,10 +121,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>金姨妈</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>王百堂</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -610,6 +617,10 @@
       </rPr>
       <t>才那姑娘是得了什么病啊？</t>
     </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>郭妈妈</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -621,7 +632,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -635,7 +646,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -656,7 +667,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -766,7 +777,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -848,9 +859,12 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1129,78 +1143,78 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.1328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.265625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="23" customFormat="1">
+    <row r="1" spans="1:20" s="23" customFormat="1" ht="18">
       <c r="A1" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="C1" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="D1" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="E1" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="F1" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="G1" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="H1" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="I1" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="J1" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="K1" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="L1" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="M1" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="M1" s="21" t="s">
+      <c r="N1" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="N1" s="21" t="s">
+      <c r="O1" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="O1" s="21" t="s">
+      <c r="P1" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="P1" s="21" t="s">
+      <c r="Q1" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="Q1" s="21" t="s">
+      <c r="R1" s="21" t="s">
         <v>58</v>
-      </c>
-      <c r="R1" s="21" t="s">
-        <v>59</v>
       </c>
       <c r="S1" s="22" t="s">
         <v>11</v>
@@ -1209,7 +1223,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="23" customFormat="1">
+    <row r="2" spans="1:20" s="23" customFormat="1" ht="18">
       <c r="A2" s="5" t="s">
         <v>15</v>
       </c>
@@ -1229,7 +1243,7 @@
         <v>17</v>
       </c>
       <c r="K2" s="25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L2" s="25" t="s">
         <v>13</v>
@@ -1337,14 +1351,14 @@
   <dimension ref="A1:I26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1374,10 +1388,10 @@
         <v>4</v>
       </c>
       <c r="I1" s="27" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="33">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1396,7 +1410,7 @@
         <v>14</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I2" s="1"/>
     </row>
@@ -1414,12 +1428,12 @@
         <v>9</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I3" s="1"/>
     </row>
@@ -1451,8 +1465,8 @@
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>23</v>
+      <c r="C5" s="29" t="s">
+        <v>65</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>22</v>
@@ -1461,7 +1475,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I5" s="1"/>
     </row>
@@ -1472,8 +1486,8 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>23</v>
+      <c r="C6" s="29" t="s">
+        <v>65</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>22</v>
@@ -1482,7 +1496,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I6" s="1"/>
     </row>
@@ -1500,7 +1514,7 @@
         <v>9</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
@@ -1514,7 +1528,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="2"/>
@@ -1522,7 +1536,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="2"/>
       <c r="H8" s="28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I8" s="1"/>
     </row>
@@ -1534,7 +1548,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>22</v>
@@ -1543,7 +1557,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="2"/>
       <c r="H9" s="14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I9" s="1"/>
     </row>
@@ -1564,7 +1578,7 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I10" s="1"/>
     </row>
@@ -1576,7 +1590,7 @@
         <v>5</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>22</v>
@@ -1585,7 +1599,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I11" s="1"/>
     </row>
@@ -1606,7 +1620,7 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I12" s="1"/>
     </row>
@@ -1618,16 +1632,16 @@
         <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I13" s="1"/>
     </row>
@@ -1639,7 +1653,7 @@
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>22</v>
@@ -1648,7 +1662,7 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I14" s="1"/>
     </row>
@@ -1660,7 +1674,7 @@
         <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>22</v>
@@ -1669,7 +1683,7 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I15" s="1"/>
     </row>
@@ -1690,7 +1704,7 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I16" s="1"/>
     </row>
@@ -1702,16 +1716,16 @@
         <v>5</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I17" s="1"/>
     </row>
@@ -1723,7 +1737,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>22</v>
@@ -1732,7 +1746,7 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I18" s="1"/>
     </row>
@@ -1753,7 +1767,7 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I19" s="1"/>
     </row>
